--- a/artfynd/A 14391-2025 artfynd.xlsx
+++ b/artfynd/A 14391-2025 artfynd.xlsx
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117505926</v>
+        <v>117505921</v>
       </c>
       <c r="B2" t="n">
-        <v>57964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102954</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +710,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -768,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117505921</v>
+        <v>117505926</v>
       </c>
       <c r="B3" t="n">
-        <v>56742</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,16 +805,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102954</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -835,11 +829,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -892,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14391-2025 artfynd.xlsx
+++ b/artfynd/A 14391-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117505921</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,8 +916,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117505926</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>